--- a/jogos_2025-04-22.xlsx
+++ b/jogos_2025-04-22.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="M5" t="n">
-        <v>3.58</v>
+        <v>2.92</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.62</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['13', '34', '43', '55', '66', '72', '90']</t>
+          <t>['25', '59']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
         <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.84</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45769.33333333334</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.81</v>
+        <v>9.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.1</v>
+        <v>2.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['25', '59']</t>
+          <t>['13', '34', '43', '55', '66', '72', '90']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG6" t="n">
         <v>1.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>3.84</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45769.33333333334</v>
@@ -1923,35 +1923,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.09</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>7.5</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.35</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.8</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['3', '51', '61', '63', '81', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.13</v>
+        <v>1.83</v>
       </c>
       <c r="AJ12" t="n">
-        <v>6</v>
+        <v>2.45</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45769.5</v>
@@ -2052,29 +2052,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45769.5</v>
@@ -2181,35 +2181,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45769.5</v>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.09</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>11.1</v>
       </c>
       <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.35</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Z15" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['3', '51', '61', '63', '81', '90+3']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.87</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.17</v>
+        <v>6</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45769.5</v>
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,23 +2604,23 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>3.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
-        <v>7.6</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q17" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['26', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '87']</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45769.54166666666</v>
@@ -2697,35 +2697,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.69</v>
+        <v>5.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.69</v>
+        <v>7.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.28</v>
+        <v>2.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['21', '43', '74', '84']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45769.54166666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
         <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['58', '60']</t>
+          <t>['19', '42', '85']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45769.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="M20" t="n">
-        <v>5.25</v>
+        <v>14</v>
       </c>
       <c r="N20" t="n">
-        <v>7.5</v>
+        <v>36</v>
       </c>
       <c r="O20" t="n">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['13', '25', '41', '52', '56', '68', '83']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.03</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['21', '43', '74', '84']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45769.54166666666</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.85</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.84</v>
+        <v>7.6</v>
       </c>
       <c r="O21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['26', '85']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['56', '87']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45769.54166666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.03</v>
       </c>
-      <c r="M22" t="n">
-        <v>14</v>
-      </c>
-      <c r="N22" t="n">
-        <v>36</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>51</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['13', '25', '41', '52', '56', '68', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>3.4</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45769.54166666666</v>
@@ -3352,48 +3352,48 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O23" t="n">
         <v>3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.3</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['19', '42', '85']</t>
+          <t>['58', '60']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45769.54166666666</v>
@@ -3471,26 +3471,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="M24" t="n">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>3.69</v>
       </c>
       <c r="O24" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
-        <v>4.33</v>
+        <v>3.22</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45769.54166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.75</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['35', '48']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['8', '78']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>5.5</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['81', '90+6']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['6', '58', '89']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.36</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45769.55555555555</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>6.75</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>1.34</v>
       </c>
       <c r="O27" t="n">
-        <v>2.01</v>
+        <v>5.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="T27" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="U27" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['35', '48']</t>
+          <t>['81', '90+6']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['8', '78']</t>
+          <t>['6', '58', '89']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45769.55555555555</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.02</v>
+        <v>2.38</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
         <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
         <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X28" t="n">
         <v>2.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.33</v>
+        <v>3.64</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
       <c r="AG28" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45769.5625</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>2.98</v>
+        <v>2.43</v>
       </c>
       <c r="O29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.1</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['58', '69', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45769.5625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,109 +4255,109 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="Z30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.36</v>
       </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['58', '69', '90+6']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AI30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45769.5625</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dibba Al Hisn</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>1.67</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
-        <v>4.75</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.05</v>
+        <v>7.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="U32" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>2.15</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45769.57291666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,16 +4642,16 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Dibba Al Hisn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8.5</v>
+        <v>1.67</v>
       </c>
       <c r="O33" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.3</v>
+        <v>2.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45769.57291666666</v>
@@ -4797,65 +4797,65 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="M34" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O34" t="n">
         <v>3</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['7', '54']</t>
+          <t>['7', '53']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45769.58333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>5.25</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.07</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="T35" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X35" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AD35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH35" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AI35" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45769.58333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Kotwica Kołobrzeg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>3</v>
       </c>
       <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="AA36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.11</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['3', '66', '81']</t>
+          <t>['18', '75', '90+9']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['31', '87']</t>
+          <t>['16', '52', '62', '90+5']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI36" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45769.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="M37" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X37" t="n">
         <v>3.5</v>
       </c>
-      <c r="N37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="Y37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45769.58333333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,19 +5287,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kotwica Kołobrzeg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>3</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>2.37</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.81</v>
+        <v>2.54</v>
       </c>
       <c r="O38" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="P38" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>3.92</v>
+        <v>5.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['3', '66', '81']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['31', '87']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI38" t="n">
         <v>2</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['18', '75', '90+9']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['16', '52', '62', '90+5']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AJ38" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45769.58333333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Y41" t="n">
         <v>2</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.82</v>
-      </c>
       <c r="Z41" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.92</v>
+        <v>3.66</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.57</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AI41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['12', '15', '54', '84']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45769.64583333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.01</v>
+        <v>3.59</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.3</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q42" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="R42" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T42" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X42" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['54', '69']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['12', '15', '54', '84']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45769.64583333334</v>
@@ -5932,16 +5932,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N43" t="n">
         <v>2.3</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.12</v>
-      </c>
       <c r="O43" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
         <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S43" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>3.19</v>
+        <v>3.81</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['54', '69']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45769.64583333334</v>
@@ -6319,19 +6319,19 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>Sloboda Tuzla</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.92</v>
+        <v>2.69</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="AC46" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.45</v>
+        <v>6.55</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45769.66666666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6463,10 +6463,10 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="n">
         <v>2.25</v>
       </c>
-      <c r="P47" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['7', '90+4']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45769.66666666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sloboda Tuzla</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="M48" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="O48" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="P48" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S48" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T48" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V48" t="n">
         <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X48" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.84</v>
+        <v>1.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '90+4']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
-        <v>6.55</v>
+        <v>1.9</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45769.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,55 +7119,55 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>3.28</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>2.24</v>
       </c>
       <c r="O52" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S52" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T52" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V52" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X52" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC52" t="n">
         <v>2.05</v>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45769.79166666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.28</v>
+        <v>1.5</v>
       </c>
       <c r="M53" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA53" t="n">
         <v>4</v>
       </c>
-      <c r="P53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AB53" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
+          <t>['31', '42', '47']</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG53" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="AH53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI53" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI53" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ53" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45769.79166666666</v>
@@ -7351,109 +7351,109 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P54" t="n">
         <v>2</v>
       </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
+      <c r="Q54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R54" t="n">
         <v>1.5</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N54" t="n">
-        <v>8</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W54" t="n">
         <v>1.44</v>
       </c>
-      <c r="S54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U54" t="n">
+      <c r="X54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
         <v>1.3</v>
       </c>
-      <c r="V54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z54" t="n">
+      <c r="AH54" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA54" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['31', '42', '47']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AI54" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ54" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45769.79166666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Carabobo</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.39</v>
+        <v>2.25</v>
       </c>
       <c r="M56" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S56" t="n">
         <v>2.3</v>
       </c>
-      <c r="O56" t="n">
-        <v>4</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T56" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="U56" t="n">
         <v>1.25</v>
       </c>
       <c r="V56" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X56" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AA56" t="n">
-        <v>5.05</v>
+        <v>5.75</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG56" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.62</v>
       </c>
-      <c r="AH56" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AI56" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45769.83333333334</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,25 +7738,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Carabobo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S57" t="n">
         <v>2.25</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T57" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="U57" t="n">
         <v>1.25</v>
       </c>
       <c r="V57" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="W57" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X57" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AA57" t="n">
-        <v>5.75</v>
+        <v>5.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD57" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AH57" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45769.83333333334</v>
@@ -8125,25 +8125,25 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8151,22 +8151,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.34</v>
+        <v>3.02</v>
       </c>
       <c r="M60" t="n">
-        <v>4.7</v>
+        <v>3.21</v>
       </c>
       <c r="N60" t="n">
-        <v>9.4</v>
+        <v>2.34</v>
       </c>
       <c r="O60" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="P60" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="R60" t="n">
         <v>1.44</v>
@@ -8181,53 +8181,53 @@
         <v>1.33</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y60" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['45+1', '67', '73']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['6', '10', '43']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AJ60" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45769.89583333334</v>
@@ -8254,25 +8254,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8280,22 +8280,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.02</v>
+        <v>1.34</v>
       </c>
       <c r="M61" t="n">
-        <v>3.21</v>
+        <v>4.7</v>
       </c>
       <c r="N61" t="n">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="O61" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="P61" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="R61" t="n">
         <v>1.44</v>
@@ -8310,53 +8310,53 @@
         <v>1.33</v>
       </c>
       <c r="V61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['45+1', '67', '73']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['6', '10', '43']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45769.89583333334</v>
